--- a/model_info/gemini_pet.xlsx
+++ b/model_info/gemini_pet.xlsx
@@ -393,7 +393,7 @@
         <v>0.06117291253740876</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.0</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.684801817253627</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.46296296296296297</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.16464091807931003</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.2253968253968254</v>
+        <v>0.6126984126984127</v>
       </c>
     </row>
     <row r="7">
@@ -785,7 +785,7 @@
         <v>0.13944303250516168</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.09166666666666667</v>
+        <v>0.5201923076923076</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.3089303090858115</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.29797979797979796</v>
+        <v>0.648989898989899</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.14638763515159098</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.758306263925723</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.616350423579598</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.10976690439199387</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.08928337394919182</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.05006166716065365</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.14180779531272109</v>
+        <v>0.5445881081826763</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.16734147039698832</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1324,7 +1324,7 @@
         <v>0.131913162402234</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.6447802197802198</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.2516476255442883</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.2341269841269841</v>
+        <v>0.5503968253968254</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>0.25215960190956377</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.31276745021304353</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.6193067022956136</v>
+        <v>0.8096533511478068</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>0.5493559589963435</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -1667,7 +1667,7 @@
         <v>0.16612051124024355</v>
       </c>
       <c r="O27" s="0" t="n">
-        <v>0.08332025117739403</v>
+        <v>0.39582679225536366</v>
       </c>
     </row>
     <row r="28">
@@ -1716,7 +1716,7 @@
         <v>0.2932054912454606</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
     </row>
     <row r="29">
@@ -1765,7 +1765,7 @@
         <v>0.45989889673063333</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.512960276082257</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="31">
@@ -1863,7 +1863,7 @@
         <v>0.30926144875469913</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.8052834631113583</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.7447703449404899</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         <v>0.25961432106483295</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
     </row>
     <row r="35">
@@ -2059,7 +2059,7 @@
         <v>0.11385999985730919</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
     </row>
     <row r="36">
@@ -2108,7 +2108,7 @@
         <v>0.3525585035076342</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.6190761910389654</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -2206,7 +2206,7 @@
         <v>0.2313182647924195</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/gemini_pet.xlsx
+++ b/model_info/gemini_pet.xlsx
@@ -393,7 +393,7 @@
         <v>0.06117291253740876</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.0</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.684801817253627</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.46296296296296297</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.16464091807931003</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.6126984126984127</v>
+        <v>0.2253968253968254</v>
       </c>
     </row>
     <row r="7">
@@ -785,7 +785,7 @@
         <v>0.13944303250516168</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.5201923076923076</v>
+        <v>0.08696581196581198</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.3089303090858115</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.648989898989899</v>
+        <v>0.29797979797979796</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.14638763515159098</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.758306263925723</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.616350423579598</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.10976690439199387</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.08928337394919182</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.05006166716065365</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.5445881081826763</v>
+        <v>0.13434422713836736</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.16734147039698832</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="19">
@@ -1324,7 +1324,7 @@
         <v>0.131913162402234</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.6447802197802198</v>
+        <v>0.35769230769230775</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.2516476255442883</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.5503968253968254</v>
+        <v>0.2029100529100529</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>0.25215960190956377</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.31276745021304353</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.8096533511478068</v>
+        <v>0.6193067022956136</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>0.5493559589963435</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
     </row>
     <row r="27">
@@ -1667,7 +1667,7 @@
         <v>0.16612051124024355</v>
       </c>
       <c r="O27" s="0" t="n">
-        <v>0.39582679225536366</v>
+        <v>0.0590185112506541</v>
       </c>
     </row>
     <row r="28">
@@ -1716,7 +1716,7 @@
         <v>0.2932054912454606</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
     </row>
     <row r="29">
@@ -1765,7 +1765,7 @@
         <v>0.45989889673063333</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.512960276082257</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="31">
@@ -1863,7 +1863,7 @@
         <v>0.30926144875469913</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.8052834631113583</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.7447703449404899</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         <v>0.25961432106483295</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
     </row>
     <row r="35">
@@ -2059,7 +2059,7 @@
         <v>0.11385999985730919</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="36">
@@ -2108,7 +2108,7 @@
         <v>0.3525585035076342</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.6190761910389654</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -2206,7 +2206,7 @@
         <v>0.2313182647924195</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
     </row>
   </sheetData>
